--- a/data/base/Backlog_37.xlsx
+++ b/data/base/Backlog_37.xlsx
@@ -1,31 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\data\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{911CA319-872F-4447-9596-B7466B540034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{298B7A61-CAB2-4976-9B81-DB76E518F7CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{65FB71B2-8070-41A1-B8B8-22F4C136B45C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{65FB71B2-8070-41A1-B8B8-22F4C136B45C}"/>
   </bookViews>
   <sheets>
     <sheet name="ITI" sheetId="1" r:id="rId1"/>
     <sheet name="SPN" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ITI!$A$1:$K$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SPN!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ITI!$A$1:$K$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SPN!$A$1:$K$6</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="28">
   <si>
     <t>Status</t>
   </si>
@@ -106,6 +106,9 @@
   </si>
   <si>
     <t>Elisandra Chaves</t>
+  </si>
+  <si>
+    <t>Resolvido</t>
   </si>
 </sst>
 </file>
@@ -453,7 +456,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -633,12 +636,34 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -655,15 +680,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1042,18 +1058,17 @@
   <dimension ref="A1:K18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5703125" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.85546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.85546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" style="8" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17" style="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="8"/>
+    <col min="1" max="1" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -1120,7 +1135,7 @@
         <v>46286</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>19</v>
@@ -1155,7 +1170,7 @@
         <v>46286</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>19</v>
@@ -1225,7 +1240,7 @@
         <v>46286</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>19</v>
@@ -1330,7 +1345,7 @@
         <v>46286</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>19</v>
@@ -1470,7 +1485,7 @@
         <v>46286</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>19</v>
@@ -1617,15 +1632,15 @@
       </c>
     </row>
     <row r="17" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="11"/>
-      <c r="K17" s="11"/>
+      <c r="A17" s="10"/>
+      <c r="K17" s="10"/>
     </row>
     <row r="18" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="11"/>
-      <c r="K18" s="11"/>
+      <c r="A18" s="10"/>
+      <c r="K18" s="10"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1" xr:uid="{B327A729-0551-401F-B555-D8AED70D606E}">
+  <autoFilter ref="A1:K16" xr:uid="{B327A729-0551-401F-B555-D8AED70D606E}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K17">
       <sortCondition ref="B1"/>
     </sortState>
@@ -1639,18 +1654,17 @@
   <dimension ref="A1:K10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.85546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5703125" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.85546875" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.5703125" style="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" style="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" style="9" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="9" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="8"/>
+    <col min="1" max="1" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.28515625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.85546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" style="8" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
@@ -1717,44 +1731,44 @@
         <v>46286</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:11" s="16" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="13">
         <v>2026</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="13">
         <v>37</v>
       </c>
-      <c r="E3" s="6">
-        <v>46286</v>
-      </c>
-      <c r="F3" s="6">
+      <c r="E3" s="14">
+        <v>46286</v>
+      </c>
+      <c r="F3" s="14">
         <v>46290</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="13">
         <v>24782</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="15">
         <v>46275.615520833337</v>
       </c>
-      <c r="I3" s="6">
-        <v>46286</v>
-      </c>
-      <c r="J3" s="5" t="s">
+      <c r="I3" s="14">
+        <v>46286</v>
+      </c>
+      <c r="J3" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="11" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1787,7 +1801,7 @@
         <v>46286</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>20</v>
@@ -1822,7 +1836,7 @@
         <v>46286</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>20</v>
@@ -1857,29 +1871,30 @@
         <v>46286</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K6" xr:uid="{1EC11F51-DC51-461C-AA02-DA399D0E5568}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>